--- a/survey_templates/029_simulation_test_survey--survey_templates.xlsx
+++ b/survey_templates/029_simulation_test_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,41 +520,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>simulation_test_survey_title</t>
+          <t>participant_feedback</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Simulation Test Survey</t>
+          <t>What was your overall experience with the simulation test?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>simulation_test_survey_category</t>
+          <t>participant_rating</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>How would you rate your experience with the simulation test?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>simulation_test_survey_description</t>
+          <t>participant_comments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>What did you think of the test's difficulty level?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,40 +584,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>simulation_test_survey_participant_id</t>
+          <t>recommend_simulation_test</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Participant ID</t>
+          <t>How likely are you to recommend this simulation test to others?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>simulation_test_survey_start_time</t>
+          <t>most_challenging_part</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Start Time</t>
+          <t>What was the most challenging part of the simulation test?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>simulation_test_survey_end_time</t>
+          <t>test_duration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>End Time</t>
+          <t>How much time did you spend on the simulation test?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,92 +653,92 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>simulation_test_survey_participant_feedback</t>
+          <t>start_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Participant Feedback</t>
+          <t>Start Time</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>simulation_test_survey_surveyor_test</t>
+          <t>finish_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Survey or Test</t>
+          <t>Finish Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>simulation_test_survey_participant_comments</t>
+          <t>num_completed_tests</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Participant Comments</t>
+          <t>How many simulation tests have you completed before?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>simulation_test_survey_instructor_name</t>
+          <t>find_useful</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Instructor Name</t>
+          <t>Do you think this simulation test was useful?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>simulation_test_survey_instructor_comments</t>
+          <t>overall_design</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Instructor Comments</t>
+          <t>What do you think about the simulation test's overall design?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>simulation_test_survey_participant_rating</t>
+          <t>take_again</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Participant Rating</t>
+          <t>Would you take this simulation test again?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>simulation_test_survey_instructor_rating</t>
+          <t>instructions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Instructor Rating</t>
+          <t>How did you find the simulation test's instructions?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,274 +814,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>simulation_test_survey_survey_completion_status</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Survey Completion Status</t>
+          <t>Do you have any suggestions for the simulation test's improvement?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_survey_type</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Survey Type</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_survey_or_test_name</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Survey or Test Name</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_participant_id</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Participant ID</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_start_time</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Start Time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_end_time</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>End Time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_participant_rating</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Participant Rating</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_instructor_rating</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Instructor Rating</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_survey_completion_status</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Survey Completion Status</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_survey_type</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Survey Type</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_survey_or_test_name</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Survey or Test Name</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>simulation_test_survey_participant_id</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Participant ID</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,204 +873,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>simulation_test_survey_category_choices</t>
+          <t>recommend_simulation_test_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>survey_templates</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Survey Templates</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>simulation_test_survey_category_choices</t>
+          <t>recommend_simulation_test_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>education_forms</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Education Forms</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>simulation_test_survey_surveyor_test_choices</t>
+          <t>recommend_simulation_test_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>simulation_test_survey_surveyor_test_choices</t>
+          <t>num_completed_tests_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>simulation_test_survey_survey_completion_status_choices</t>
+          <t>num_completed_tests_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>simulation_test_survey_survey_completion_status_choices</t>
+          <t>num_completed_tests_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>simulation_test_survey_survey_type_choices</t>
+          <t>num_completed_tests_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>4_or_more</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>4 or more</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>simulation_test_survey_survey_type_choices</t>
+          <t>find_useful_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>simulation_test_survey_survey_completion_status_choices</t>
+          <t>find_useful_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>simulation_test_survey_survey_completion_status_choices</t>
+          <t>find_useful_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>simulation_test_survey_survey_type_choices</t>
+          <t>take_again_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>simulation_test_survey_survey_type_choices</t>
+          <t>take_again_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>take_again_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>unsure</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
